--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763471</v>
+        <v>123763552</v>
       </c>
       <c r="B2" t="n">
-        <v>57487</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517621</v>
+        <v>517614</v>
       </c>
       <c r="R2" t="n">
-        <v>6702557</v>
+        <v>6702545</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763328</v>
+        <v>123763541</v>
       </c>
       <c r="B3" t="n">
-        <v>90983</v>
+        <v>91006</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -833,10 +828,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517372</v>
+        <v>517625</v>
       </c>
       <c r="R3" t="n">
-        <v>6702650</v>
+        <v>6702551</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -896,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763409</v>
+        <v>123763328</v>
       </c>
       <c r="B4" t="n">
-        <v>90983</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517551</v>
+        <v>517372</v>
       </c>
       <c r="R4" t="n">
-        <v>6702581</v>
+        <v>6702650</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763346</v>
+        <v>123763431</v>
       </c>
       <c r="B5" t="n">
-        <v>91001</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,30 +1009,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1045,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517378</v>
+        <v>517587</v>
       </c>
       <c r="R5" t="n">
-        <v>6702642</v>
+        <v>6702560</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1089,7 +1089,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1108,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763599</v>
+        <v>123763346</v>
       </c>
       <c r="B6" t="n">
-        <v>57503</v>
+        <v>91006</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,31 +1123,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1156,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517577</v>
+        <v>517378</v>
       </c>
       <c r="R6" t="n">
-        <v>6702530</v>
+        <v>6702642</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1194,17 +1188,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1223,10 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763644</v>
+        <v>123763608</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1235,25 +1225,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1261,7 +1251,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1271,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517717</v>
+        <v>517568</v>
       </c>
       <c r="R7" t="n">
-        <v>6702484</v>
+        <v>6702512</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1307,11 +1297,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,10 +1323,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763552</v>
+        <v>123763439</v>
       </c>
       <c r="B8" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,10 +1371,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517614</v>
+        <v>517616</v>
       </c>
       <c r="R8" t="n">
-        <v>6702545</v>
+        <v>6702550</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1448,10 +1433,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763439</v>
+        <v>123763644</v>
       </c>
       <c r="B9" t="n">
-        <v>56697</v>
+        <v>57506</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1460,25 +1445,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1486,7 +1471,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1496,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517616</v>
+        <v>517717</v>
       </c>
       <c r="R9" t="n">
-        <v>6702550</v>
+        <v>6702484</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,6 +1517,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763417</v>
+        <v>123763471</v>
       </c>
       <c r="B10" t="n">
-        <v>56697</v>
+        <v>57490</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,25 +1560,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1596,7 +1586,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1606,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517566</v>
+        <v>517621</v>
       </c>
       <c r="R10" t="n">
-        <v>6702581</v>
+        <v>6702557</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1642,6 +1632,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1668,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763390</v>
+        <v>123763417</v>
       </c>
       <c r="B11" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517472</v>
+        <v>517566</v>
       </c>
       <c r="R11" t="n">
-        <v>6702628</v>
+        <v>6702581</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1778,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763541</v>
+        <v>123763409</v>
       </c>
       <c r="B12" t="n">
-        <v>91001</v>
+        <v>90988</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1794,21 +1789,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,10 +1816,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517625</v>
+        <v>517551</v>
       </c>
       <c r="R12" t="n">
-        <v>6702551</v>
+        <v>6702581</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1884,10 +1879,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763431</v>
+        <v>123763390</v>
       </c>
       <c r="B13" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517587</v>
+        <v>517472</v>
       </c>
       <c r="R13" t="n">
-        <v>6702560</v>
+        <v>6702628</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1994,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763608</v>
+        <v>123763599</v>
       </c>
       <c r="B14" t="n">
-        <v>56697</v>
+        <v>57506</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,25 +2001,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,7 +2027,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2042,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517568</v>
+        <v>517577</v>
       </c>
       <c r="R14" t="n">
-        <v>6702512</v>
+        <v>6702530</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2078,6 +2073,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763552</v>
+        <v>123763471</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517614</v>
+        <v>517621</v>
       </c>
       <c r="R2" t="n">
-        <v>6702545</v>
+        <v>6702557</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763541</v>
+        <v>123763439</v>
       </c>
       <c r="B3" t="n">
-        <v>91006</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,30 +802,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517625</v>
+        <v>517616</v>
       </c>
       <c r="R3" t="n">
-        <v>6702551</v>
+        <v>6702550</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -872,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -891,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763328</v>
+        <v>123763552</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,30 +912,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -934,10 +948,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517372</v>
+        <v>517614</v>
       </c>
       <c r="R4" t="n">
-        <v>6702650</v>
+        <v>6702545</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -978,7 +992,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -997,7 +1010,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763431</v>
+        <v>123763417</v>
       </c>
       <c r="B5" t="n">
         <v>56700</v>
@@ -1045,10 +1058,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517587</v>
+        <v>517566</v>
       </c>
       <c r="R5" t="n">
-        <v>6702560</v>
+        <v>6702581</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,10 +1120,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763346</v>
+        <v>123763541</v>
       </c>
       <c r="B6" t="n">
-        <v>91006</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517378</v>
+        <v>517625</v>
       </c>
       <c r="R6" t="n">
-        <v>6702642</v>
+        <v>6702551</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1213,10 +1226,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763608</v>
+        <v>123763644</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,25 +1238,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1251,7 +1264,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1261,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517568</v>
+        <v>517717</v>
       </c>
       <c r="R7" t="n">
-        <v>6702512</v>
+        <v>6702484</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1297,6 +1310,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,7 +1341,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763439</v>
+        <v>123763431</v>
       </c>
       <c r="B8" t="n">
         <v>56700</v>
@@ -1371,10 +1389,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517616</v>
+        <v>517587</v>
       </c>
       <c r="R8" t="n">
-        <v>6702550</v>
+        <v>6702560</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1433,10 +1451,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763644</v>
+        <v>123763409</v>
       </c>
       <c r="B9" t="n">
-        <v>57506</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1449,31 +1467,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1481,10 +1494,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517717</v>
+        <v>517551</v>
       </c>
       <c r="R9" t="n">
-        <v>6702484</v>
+        <v>6702581</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1519,17 +1532,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763471</v>
+        <v>123763328</v>
       </c>
       <c r="B10" t="n">
-        <v>57490</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,31 +1573,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1596,10 +1600,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517621</v>
+        <v>517372</v>
       </c>
       <c r="R10" t="n">
-        <v>6702557</v>
+        <v>6702650</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1634,17 +1638,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763417</v>
+        <v>123763346</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>91008</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,35 +1675,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1711,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517566</v>
+        <v>517378</v>
       </c>
       <c r="R11" t="n">
-        <v>6702581</v>
+        <v>6702642</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1755,6 +1750,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1773,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763409</v>
+        <v>123763390</v>
       </c>
       <c r="B12" t="n">
-        <v>90988</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,30 +1781,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1816,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517551</v>
+        <v>517472</v>
       </c>
       <c r="R12" t="n">
-        <v>6702581</v>
+        <v>6702628</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1860,7 +1861,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763390</v>
+        <v>123763608</v>
       </c>
       <c r="B13" t="n">
         <v>56700</v>
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517472</v>
+        <v>517568</v>
       </c>
       <c r="R13" t="n">
-        <v>6702628</v>
+        <v>6702512</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1992,7 +1992,7 @@
         <v>123763599</v>
       </c>
       <c r="B14" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763471</v>
+        <v>123763409</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517621</v>
+        <v>517551</v>
       </c>
       <c r="R2" t="n">
-        <v>6702557</v>
+        <v>6702581</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -761,17 +756,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763439</v>
+        <v>123763328</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,35 +793,30 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517616</v>
+        <v>517372</v>
       </c>
       <c r="R3" t="n">
-        <v>6702550</v>
+        <v>6702650</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -882,6 +868,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763552</v>
+        <v>123763608</v>
       </c>
       <c r="B4" t="n">
         <v>56700</v>
@@ -948,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517614</v>
+        <v>517568</v>
       </c>
       <c r="R4" t="n">
-        <v>6702545</v>
+        <v>6702512</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -1010,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763417</v>
+        <v>123763471</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,25 +1009,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1048,7 +1035,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1058,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517566</v>
+        <v>517621</v>
       </c>
       <c r="R5" t="n">
-        <v>6702581</v>
+        <v>6702557</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,6 +1081,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1120,7 +1112,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763541</v>
+        <v>123763346</v>
       </c>
       <c r="B6" t="n">
         <v>91008</v>
@@ -1163,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517625</v>
+        <v>517378</v>
       </c>
       <c r="R6" t="n">
-        <v>6702551</v>
+        <v>6702642</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1226,10 +1218,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763644</v>
+        <v>123763541</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1242,31 +1234,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517717</v>
+        <v>517625</v>
       </c>
       <c r="R7" t="n">
-        <v>6702484</v>
+        <v>6702551</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1312,17 +1299,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1341,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763431</v>
+        <v>123763599</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,25 +1336,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,7 +1362,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1389,10 +1372,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517587</v>
+        <v>517577</v>
       </c>
       <c r="R8" t="n">
-        <v>6702560</v>
+        <v>6702530</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1425,6 +1408,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1451,10 +1439,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763409</v>
+        <v>123763644</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1467,26 +1455,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1494,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517551</v>
+        <v>517717</v>
       </c>
       <c r="R9" t="n">
-        <v>6702581</v>
+        <v>6702484</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1532,13 +1525,17 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1557,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763328</v>
+        <v>123763390</v>
       </c>
       <c r="B10" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1569,30 +1566,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1600,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517372</v>
+        <v>517472</v>
       </c>
       <c r="R10" t="n">
-        <v>6702650</v>
+        <v>6702628</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1644,7 +1646,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1663,10 +1664,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763346</v>
+        <v>123763417</v>
       </c>
       <c r="B11" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,30 +1676,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1712,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517378</v>
+        <v>517566</v>
       </c>
       <c r="R11" t="n">
-        <v>6702642</v>
+        <v>6702581</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1750,7 +1756,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,7 +1774,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763390</v>
+        <v>123763431</v>
       </c>
       <c r="B12" t="n">
         <v>56700</v>
@@ -1817,10 +1822,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517472</v>
+        <v>517587</v>
       </c>
       <c r="R12" t="n">
-        <v>6702628</v>
+        <v>6702560</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1879,7 +1884,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763608</v>
+        <v>123763439</v>
       </c>
       <c r="B13" t="n">
         <v>56700</v>
@@ -1927,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517568</v>
+        <v>517616</v>
       </c>
       <c r="R13" t="n">
-        <v>6702512</v>
+        <v>6702550</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1989,10 +1994,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763599</v>
+        <v>123763552</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2001,25 +2006,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2027,7 +2032,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2037,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517577</v>
+        <v>517614</v>
       </c>
       <c r="R14" t="n">
-        <v>6702530</v>
+        <v>6702545</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2073,11 +2078,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763608</v>
+        <v>123763471</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +925,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517568</v>
+        <v>517621</v>
       </c>
       <c r="R4" t="n">
-        <v>6702512</v>
+        <v>6702557</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -971,6 +971,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,10 +1002,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763471</v>
+        <v>123763608</v>
       </c>
       <c r="B5" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,25 +1014,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,7 +1040,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1045,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517621</v>
+        <v>517568</v>
       </c>
       <c r="R5" t="n">
-        <v>6702557</v>
+        <v>6702512</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1081,11 +1086,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763409</v>
+        <v>123763328</v>
       </c>
       <c r="B2" t="n">
         <v>90990</v>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517551</v>
+        <v>517372</v>
       </c>
       <c r="R2" t="n">
-        <v>6702581</v>
+        <v>6702650</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763328</v>
+        <v>123763409</v>
       </c>
       <c r="B3" t="n">
         <v>90990</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517372</v>
+        <v>517551</v>
       </c>
       <c r="R3" t="n">
-        <v>6702650</v>
+        <v>6702581</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763471</v>
+        <v>123763439</v>
       </c>
       <c r="B4" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +899,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +925,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517621</v>
+        <v>517616</v>
       </c>
       <c r="R4" t="n">
-        <v>6702557</v>
+        <v>6702550</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -971,11 +971,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1002,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763608</v>
+        <v>123763346</v>
       </c>
       <c r="B5" t="n">
-        <v>56700</v>
+        <v>91008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,35 +1009,30 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1040,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517568</v>
+        <v>517378</v>
       </c>
       <c r="R5" t="n">
-        <v>6702512</v>
+        <v>6702642</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1094,6 +1084,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1112,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763346</v>
+        <v>123763417</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1124,30 +1115,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1155,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517378</v>
+        <v>517566</v>
       </c>
       <c r="R6" t="n">
-        <v>6702642</v>
+        <v>6702581</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1199,7 +1195,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1439,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763644</v>
+        <v>123763552</v>
       </c>
       <c r="B9" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1451,25 +1446,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1477,7 +1472,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1487,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517717</v>
+        <v>517614</v>
       </c>
       <c r="R9" t="n">
-        <v>6702484</v>
+        <v>6702545</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,11 +1518,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763390</v>
+        <v>123763644</v>
       </c>
       <c r="B10" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,25 +1556,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1592,7 +1582,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1602,10 +1592,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517472</v>
+        <v>517717</v>
       </c>
       <c r="R10" t="n">
-        <v>6702628</v>
+        <v>6702484</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1638,6 +1628,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1664,7 +1659,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763417</v>
+        <v>123763390</v>
       </c>
       <c r="B11" t="n">
         <v>56700</v>
@@ -1712,10 +1707,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517566</v>
+        <v>517472</v>
       </c>
       <c r="R11" t="n">
-        <v>6702581</v>
+        <v>6702628</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1774,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763431</v>
+        <v>123763471</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>57491</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1786,25 +1781,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,7 +1807,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1822,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517587</v>
+        <v>517621</v>
       </c>
       <c r="R12" t="n">
-        <v>6702560</v>
+        <v>6702557</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1858,6 +1853,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,7 +1884,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763439</v>
+        <v>123763608</v>
       </c>
       <c r="B13" t="n">
         <v>56700</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517616</v>
+        <v>517568</v>
       </c>
       <c r="R13" t="n">
-        <v>6702550</v>
+        <v>6702512</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763552</v>
+        <v>123763431</v>
       </c>
       <c r="B14" t="n">
         <v>56700</v>
@@ -2042,10 +2042,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517614</v>
+        <v>517587</v>
       </c>
       <c r="R14" t="n">
-        <v>6702545</v>
+        <v>6702560</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763328</v>
+        <v>123763346</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>91008</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517372</v>
+        <v>517378</v>
       </c>
       <c r="R2" t="n">
-        <v>6702650</v>
+        <v>6702642</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763409</v>
+        <v>123763552</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,30 +793,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -824,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517551</v>
+        <v>517614</v>
       </c>
       <c r="R3" t="n">
-        <v>6702581</v>
+        <v>6702545</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,7 +873,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763439</v>
+        <v>123763644</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,25 +903,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,7 +929,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -935,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517616</v>
+        <v>517717</v>
       </c>
       <c r="R4" t="n">
-        <v>6702550</v>
+        <v>6702484</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -971,6 +975,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -997,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763346</v>
+        <v>123763390</v>
       </c>
       <c r="B5" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,30 +1018,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1040,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517378</v>
+        <v>517472</v>
       </c>
       <c r="R5" t="n">
-        <v>6702642</v>
+        <v>6702628</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1084,7 +1098,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1103,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763417</v>
+        <v>123763541</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,35 +1128,30 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1151,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517566</v>
+        <v>517625</v>
       </c>
       <c r="R6" t="n">
-        <v>6702581</v>
+        <v>6702551</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1195,6 +1203,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1213,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763541</v>
+        <v>123763431</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1225,30 +1234,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1256,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517625</v>
+        <v>517587</v>
       </c>
       <c r="R7" t="n">
-        <v>6702551</v>
+        <v>6702560</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1300,7 +1314,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1319,10 +1332,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763599</v>
+        <v>123763608</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1331,25 +1344,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,7 +1370,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
@@ -1367,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517577</v>
+        <v>517568</v>
       </c>
       <c r="R8" t="n">
-        <v>6702530</v>
+        <v>6702512</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1403,11 +1416,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763552</v>
+        <v>123763409</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1446,35 +1454,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1482,10 +1485,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517614</v>
+        <v>517551</v>
       </c>
       <c r="R9" t="n">
-        <v>6702545</v>
+        <v>6702581</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1526,6 +1529,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1544,10 +1548,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763644</v>
+        <v>123763471</v>
       </c>
       <c r="B10" t="n">
-        <v>57507</v>
+        <v>57491</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1560,16 +1564,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1582,7 +1586,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1592,10 +1596,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517717</v>
+        <v>517621</v>
       </c>
       <c r="R10" t="n">
-        <v>6702484</v>
+        <v>6702557</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1632,7 +1636,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Hack nedtill på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1659,10 +1663,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763390</v>
+        <v>123763328</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>90990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1671,35 +1675,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1707,10 +1706,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517472</v>
+        <v>517372</v>
       </c>
       <c r="R11" t="n">
-        <v>6702628</v>
+        <v>6702650</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1751,6 +1750,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763471</v>
+        <v>123763439</v>
       </c>
       <c r="B12" t="n">
-        <v>57491</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1781,25 +1781,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1807,7 +1807,7 @@
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517621</v>
+        <v>517616</v>
       </c>
       <c r="R12" t="n">
-        <v>6702557</v>
+        <v>6702550</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1853,11 +1853,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,7 +1879,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763608</v>
+        <v>123763417</v>
       </c>
       <c r="B13" t="n">
         <v>56700</v>
@@ -1932,10 +1927,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517568</v>
+        <v>517566</v>
       </c>
       <c r="R13" t="n">
-        <v>6702512</v>
+        <v>6702581</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1994,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763431</v>
+        <v>123763599</v>
       </c>
       <c r="B14" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2006,25 +2001,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,7 +2027,7 @@
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
@@ -2042,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517587</v>
+        <v>517577</v>
       </c>
       <c r="R14" t="n">
-        <v>6702560</v>
+        <v>6702530</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2078,6 +2073,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763346</v>
+        <v>123763409</v>
       </c>
       <c r="B2" t="n">
-        <v>91008</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517378</v>
+        <v>517551</v>
       </c>
       <c r="R2" t="n">
-        <v>6702642</v>
+        <v>6702581</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763552</v>
+        <v>123763608</v>
       </c>
       <c r="B3" t="n">
         <v>56700</v>
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517614</v>
+        <v>517568</v>
       </c>
       <c r="R3" t="n">
-        <v>6702545</v>
+        <v>6702512</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763644</v>
+        <v>123763328</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>90990</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,31 +907,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -939,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517717</v>
+        <v>517372</v>
       </c>
       <c r="R4" t="n">
-        <v>6702484</v>
+        <v>6702650</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -977,17 +972,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,7 +997,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763390</v>
+        <v>123763417</v>
       </c>
       <c r="B5" t="n">
         <v>56700</v>
@@ -1054,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517472</v>
+        <v>517566</v>
       </c>
       <c r="R5" t="n">
-        <v>6702628</v>
+        <v>6702581</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1116,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763541</v>
+        <v>123763471</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>57491</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,26 +1123,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1155,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517625</v>
+        <v>517621</v>
       </c>
       <c r="R6" t="n">
-        <v>6702551</v>
+        <v>6702557</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1197,13 +1193,17 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763431</v>
+        <v>123763390</v>
       </c>
       <c r="B7" t="n">
         <v>56700</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517587</v>
+        <v>517472</v>
       </c>
       <c r="R7" t="n">
-        <v>6702560</v>
+        <v>6702628</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763608</v>
+        <v>123763552</v>
       </c>
       <c r="B8" t="n">
         <v>56700</v>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517568</v>
+        <v>517614</v>
       </c>
       <c r="R8" t="n">
-        <v>6702512</v>
+        <v>6702545</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763409</v>
+        <v>123763599</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,26 +1458,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1485,10 +1490,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517551</v>
+        <v>517577</v>
       </c>
       <c r="R9" t="n">
-        <v>6702581</v>
+        <v>6702530</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1523,13 +1528,17 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1548,10 +1557,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763471</v>
+        <v>123763644</v>
       </c>
       <c r="B10" t="n">
-        <v>57491</v>
+        <v>57507</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1564,16 +1573,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1586,7 +1595,7 @@
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1596,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517621</v>
+        <v>517717</v>
       </c>
       <c r="R10" t="n">
-        <v>6702557</v>
+        <v>6702484</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1636,7 +1645,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763328</v>
+        <v>123763431</v>
       </c>
       <c r="B11" t="n">
-        <v>90990</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,30 +1684,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1720,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517372</v>
+        <v>517587</v>
       </c>
       <c r="R11" t="n">
-        <v>6702650</v>
+        <v>6702560</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1750,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1879,10 +1892,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763417</v>
+        <v>123763541</v>
       </c>
       <c r="B13" t="n">
-        <v>56700</v>
+        <v>91008</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,35 +1904,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -1927,10 +1935,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517566</v>
+        <v>517625</v>
       </c>
       <c r="R13" t="n">
-        <v>6702581</v>
+        <v>6702551</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>
@@ -1971,6 +1979,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1989,10 +1998,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123763599</v>
+        <v>123763346</v>
       </c>
       <c r="B14" t="n">
-        <v>57507</v>
+        <v>91008</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2005,31 +2014,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2037,10 +2041,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>517577</v>
+        <v>517378</v>
       </c>
       <c r="R14" t="n">
-        <v>6702530</v>
+        <v>6702642</v>
       </c>
       <c r="S14" t="n">
         <v>50</v>
@@ -2075,17 +2079,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -1222,7 +1222,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763390</v>
+        <v>123763552</v>
       </c>
       <c r="B7" t="n">
         <v>56700</v>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517472</v>
+        <v>517614</v>
       </c>
       <c r="R7" t="n">
-        <v>6702628</v>
+        <v>6702545</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,7 +1332,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763552</v>
+        <v>123763390</v>
       </c>
       <c r="B8" t="n">
         <v>56700</v>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517614</v>
+        <v>517472</v>
       </c>
       <c r="R8" t="n">
-        <v>6702545</v>
+        <v>6702628</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763552</v>
+        <v>123763599</v>
       </c>
       <c r="B2" t="n">
-        <v>56722</v>
+        <v>57529</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517614</v>
+        <v>517577</v>
       </c>
       <c r="R2" t="n">
-        <v>6702545</v>
+        <v>6702530</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -759,6 +759,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,10 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763471</v>
+        <v>123763390</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56722</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,25 +802,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -823,7 +828,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -833,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517621</v>
+        <v>517472</v>
       </c>
       <c r="R3" t="n">
-        <v>6702557</v>
+        <v>6702628</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,11 +874,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763417</v>
+        <v>123763409</v>
       </c>
       <c r="B4" t="n">
-        <v>56722</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,35 +912,30 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -948,7 +943,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517566</v>
+        <v>517551</v>
       </c>
       <c r="R4" t="n">
         <v>6702581</v>
@@ -992,6 +987,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1010,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763541</v>
+        <v>123763417</v>
       </c>
       <c r="B5" t="n">
-        <v>91030</v>
+        <v>56722</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,30 +1018,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1053,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517625</v>
+        <v>517566</v>
       </c>
       <c r="R5" t="n">
-        <v>6702551</v>
+        <v>6702581</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1097,7 +1098,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763346</v>
+        <v>123763644</v>
       </c>
       <c r="B6" t="n">
-        <v>91030</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,26 +1132,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517378</v>
+        <v>517717</v>
       </c>
       <c r="R6" t="n">
-        <v>6702642</v>
+        <v>6702484</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1197,13 +1202,17 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1222,7 +1231,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763390</v>
+        <v>123763431</v>
       </c>
       <c r="B7" t="n">
         <v>56722</v>
@@ -1270,10 +1279,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517472</v>
+        <v>517587</v>
       </c>
       <c r="R7" t="n">
-        <v>6702628</v>
+        <v>6702560</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1332,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763599</v>
+        <v>123763541</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1348,31 +1357,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1380,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517577</v>
+        <v>517625</v>
       </c>
       <c r="R8" t="n">
-        <v>6702530</v>
+        <v>6702551</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1418,17 +1422,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763439</v>
+        <v>123763471</v>
       </c>
       <c r="B9" t="n">
-        <v>56722</v>
+        <v>57513</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1459,25 +1459,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,7 +1485,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517616</v>
+        <v>517621</v>
       </c>
       <c r="R9" t="n">
-        <v>6702550</v>
+        <v>6702557</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1531,6 +1531,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,10 +1562,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763409</v>
+        <v>123763346</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1573,21 +1578,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1600,10 +1605,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517551</v>
+        <v>517378</v>
       </c>
       <c r="R10" t="n">
-        <v>6702581</v>
+        <v>6702642</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1663,10 +1668,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763328</v>
+        <v>123763439</v>
       </c>
       <c r="B11" t="n">
-        <v>91012</v>
+        <v>56722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1675,30 +1680,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1706,10 +1716,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517372</v>
+        <v>517616</v>
       </c>
       <c r="R11" t="n">
-        <v>6702650</v>
+        <v>6702550</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1750,7 +1760,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1778,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763644</v>
+        <v>123763328</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,31 +1794,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1817,10 +1821,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517717</v>
+        <v>517372</v>
       </c>
       <c r="R12" t="n">
-        <v>6702484</v>
+        <v>6702650</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1855,17 +1859,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1884,7 +1884,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123763431</v>
+        <v>123763552</v>
       </c>
       <c r="B13" t="n">
         <v>56722</v>
@@ -1932,10 +1932,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>517587</v>
+        <v>517614</v>
       </c>
       <c r="R13" t="n">
-        <v>6702560</v>
+        <v>6702545</v>
       </c>
       <c r="S13" t="n">
         <v>50</v>

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123763599</v>
+        <v>123763328</v>
       </c>
       <c r="B2" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,31 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -723,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>517577</v>
+        <v>517372</v>
       </c>
       <c r="R2" t="n">
-        <v>6702530</v>
+        <v>6702650</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -761,17 +751,13 @@
           <t>2025-04-04</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Hack nedtill på gran</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -790,47 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123763390</v>
+        <v>123763409</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -838,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>517472</v>
+        <v>517551</v>
       </c>
       <c r="R3" t="n">
-        <v>6702628</v>
+        <v>6702581</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -882,6 +858,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,42 +877,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123763409</v>
+        <v>123763599</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -943,10 +920,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>517551</v>
+        <v>517577</v>
       </c>
       <c r="R4" t="n">
-        <v>6702581</v>
+        <v>6702530</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -981,13 +958,17 @@
           <t>2025-04-04</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,15 +987,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123763417</v>
+        <v>123763644</v>
       </c>
       <c r="B5" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +998,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,7 +1020,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1054,10 +1030,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>517566</v>
+        <v>517717</v>
       </c>
       <c r="R5" t="n">
-        <v>6702581</v>
+        <v>6702484</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1090,6 +1066,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-04-04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Hack nedtill på gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,15 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123763644</v>
+        <v>123763471</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1132,16 +1108,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1154,7 +1130,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1164,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>517717</v>
+        <v>517621</v>
       </c>
       <c r="R6" t="n">
-        <v>6702484</v>
+        <v>6702557</v>
       </c>
       <c r="S6" t="n">
         <v>50</v>
@@ -1204,7 +1180,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hack nedtill på gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,15 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123763431</v>
+        <v>123763390</v>
       </c>
       <c r="B7" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1279,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>517587</v>
+        <v>517472</v>
       </c>
       <c r="R7" t="n">
-        <v>6702560</v>
+        <v>6702628</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1341,42 +1312,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123763541</v>
+        <v>123763417</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,10 +1355,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>517625</v>
+        <v>517566</v>
       </c>
       <c r="R8" t="n">
-        <v>6702551</v>
+        <v>6702581</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1428,7 +1399,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1447,37 +1417,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123763471</v>
+        <v>123763431</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1485,7 +1450,7 @@
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1495,10 +1460,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>517621</v>
+        <v>517587</v>
       </c>
       <c r="R9" t="n">
-        <v>6702557</v>
+        <v>6702560</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1531,11 +1496,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,42 +1522,42 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123763346</v>
+        <v>123763439</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1605,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>517378</v>
+        <v>517616</v>
       </c>
       <c r="R10" t="n">
-        <v>6702642</v>
+        <v>6702550</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1649,7 +1609,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1668,15 +1627,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123763439</v>
+        <v>123763552</v>
       </c>
       <c r="B11" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1716,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>517616</v>
+        <v>517614</v>
       </c>
       <c r="R11" t="n">
-        <v>6702550</v>
+        <v>6702545</v>
       </c>
       <c r="S11" t="n">
         <v>50</v>
@@ -1778,42 +1732,42 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123763328</v>
+        <v>123763608</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1821,10 +1775,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>517372</v>
+        <v>517568</v>
       </c>
       <c r="R12" t="n">
-        <v>6702650</v>
+        <v>6702512</v>
       </c>
       <c r="S12" t="n">
         <v>50</v>
@@ -1865,7 +1819,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1881,226 +1834,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>123763552</v>
-      </c>
-      <c r="B13" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Boberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>517614</v>
-      </c>
-      <c r="R13" t="n">
-        <v>6702545</v>
-      </c>
-      <c r="S13" t="n">
-        <v>50</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>123763608</v>
-      </c>
-      <c r="B14" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>100138</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Tjäder</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tetrao urogallus</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Boberget, Dlr</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>517568</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6702512</v>
-      </c>
-      <c r="S14" t="n">
-        <v>50</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Borlänge</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Stora Tuna</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2025-04-04</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Anna-Lena Thommson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10712-2025 artfynd.xlsx
+++ b/artfynd/A 10712-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763328</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763409</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,6 +999,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763599</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1094,6 +1114,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763644</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763471</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1309,6 +1339,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763390</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763417</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763431</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763439</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1729,6 +1779,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763552</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,8 +1889,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123763608</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>